--- a/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
+++ b/downloads/indicadores/CONSUMO/CONSUMO_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -542,7 +542,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf · Fecha de publicación: 5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="AP6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ6" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="AP7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ7" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="AP8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ8" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AP9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ9" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AP10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ10" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="AP11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ11" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="AP12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ12" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="AP13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ13" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="AP14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ14" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="AP15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ15" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="AP16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ16" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="AP17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ17" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2535,12 +2535,12 @@
       </c>
       <c r="AP18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ18" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="AP20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ20" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="AP21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ21" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3051,12 @@
       </c>
       <c r="AP22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ22" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AP23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ23" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="AP24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ24" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="AP25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ25" s="11" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3615,12 +3615,153 @@
       </c>
       <c r="AP26" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_09.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
         </is>
       </c>
       <c r="AQ26" s="8" t="inlineStr">
         <is>
-          <t>4 de septiembre de 2026</t>
+          <t>5 de octubre de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="O27" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="P27" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="R27" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S27" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="T27" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="U27" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V27" s="10" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W27" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="X27" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Y27" s="10" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="Z27" s="10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AA27" s="10" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AB27" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AC27" s="10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AD27" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="AE27" s="10" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="AF27" s="10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AG27" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AH27" s="10" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AI27" s="10" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AJ27" s="10" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="AK27" s="10" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="AL27" s="10" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="AM27" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN27" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="AO27" s="11" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="AP27" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_10.pdf</t>
+        </is>
+      </c>
+      <c r="AQ27" s="11" t="inlineStr">
+        <is>
+          <t>5 de octubre de 2026</t>
         </is>
       </c>
     </row>
